--- a/projects/questions_template.xlsx
+++ b/projects/questions_template.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to fill" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -831,6 +832,11 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="F2:F500" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Not in the list" error="Pick one of the choices from the dropdown list." prompt="Pick the right option: A, B, C or D" type="list">
+      <formula1>=Lists!$A$1:$A$8</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -841,7 +847,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -857,42 +863,119 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Options: 2 to 4. Leave Option C / D empty for fewer options.</t>
+          <t>Correct has a dropdown list: click the cell and pick A, B, C or D (or أ ب ج د).</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Correct: A, B, C or D (or أ ب ج د, or 1-4, or the exact text of the right option).</t>
+          <t>Options: 2 to 4. Leave Option C / D empty for fewer options.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Explanation: optional, shown after the answer is revealed.</t>
+          <t>Correct: A, B, C or D (or أ ب ج د, or 1-4, or the exact text of the right option).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Audio columns are optional. Write the clip's file name (q1.mp3) and upload the clips in the app,</t>
+          <t>Explanation: optional, shown after the answer is revealed.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>or write a path relative to the 'Audio folder' you set in the app, or a full path (C:\quiz\q1.mp3).</t>
+          <t>Audio columns are optional. Write the clip's file name (q1.mp3) and upload the clips in the app,</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>or write a path relative to the 'Audio folder' you set in the app, or a full path (C:\quiz\q1.mp3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>In the app choose how many questions go in each video: 30 rows with 5 per video makes 6 videos.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>أ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ب</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ج</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>د</t>
         </is>
       </c>
     </row>
